--- a/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_snowbreakspine[Mod道具信息-SnowbreakSpine].xlsx
+++ b/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info_snowbreakspine[Mod道具信息-SnowbreakSpine].xlsx
@@ -653,13 +653,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001_01_SkeletonData&amp;ui_show_data:0.2486;0,0&amp;ui_show_idle_anim:sp_girl001_01_stand</t>
@@ -673,7 +672,6 @@
           <t>尘白幻化药(Snowbreak Girl001/01/Girl001_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>1</t>
@@ -701,13 +699,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001_02_SkeletonData&amp;ui_show_data:0.2487;0,0&amp;ui_show_idle_anim:sp_girl001_stand</t>
@@ -721,7 +718,6 @@
           <t>尘白幻化药(Snowbreak Girl001/02/Girl001_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>1</t>
@@ -749,13 +745,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001_SkeletonData&amp;ui_show_data:0.249;0,0&amp;ui_show_idle_anim:sp_girl001_stand</t>
@@ -769,7 +764,6 @@
           <t>尘白幻化药(Snowbreak Girl001/Girl001/Girl001_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>1</t>
@@ -797,13 +791,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001a_SkeletonData&amp;ui_show_data:0.2339;0,0&amp;ui_show_idle_anim:sp_girl001_stand</t>
@@ -817,7 +810,6 @@
           <t>尘白幻化药(Snowbreak Girl001/a/Girl001a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>1</t>
@@ -845,13 +837,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001a_03_SkeletonData&amp;ui_show_data:0.1381;0,0&amp;ui_show_idle_anim:sp_girl001a_03_gachastand</t>
@@ -865,7 +856,6 @@
           <t>尘白幻化药(Snowbreak Girl001/a_03/Girl001a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>1</t>
@@ -893,13 +883,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001b_SkeletonData&amp;ui_show_data:0.065;0,0&amp;ui_show_idle_anim:sp_girl001b_gachastand</t>
@@ -913,7 +902,6 @@
           <t>尘白幻化药(Snowbreak Girl001/b/Girl001b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>1</t>
@@ -941,13 +929,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001b_02_SkeletonData&amp;ui_show_data:0.0935;0,0&amp;ui_show_idle_anim:sp_girl001b_02_gachastand</t>
@@ -961,7 +948,6 @@
           <t>尘白幻化药(Snowbreak Girl001/b_02/Girl001b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>1</t>
@@ -989,13 +975,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>ui_show_res:Girl001b_lv2_SkeletonData&amp;ui_show_data:0.1791;0,0&amp;ui_show_idle_anim:sp_girl001b_lv2_stand</t>
@@ -1009,7 +994,6 @@
           <t>尘白幻化药(Snowbreak Girl001/b_lv2/Girl001b_lv2_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>1</t>
@@ -1037,13 +1021,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002_01_SkeletonData&amp;ui_show_data:0.2275;0,0&amp;ui_show_idle_anim:sp_girl002_stand</t>
@@ -1057,7 +1040,6 @@
           <t>尘白幻化药(Snowbreak Girl002/01/Girl002_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1085,13 +1067,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002_SkeletonData&amp;ui_show_data:0.2273;0,0&amp;ui_show_idle_anim:sp_girl002_stand</t>
@@ -1105,7 +1086,6 @@
           <t>尘白幻化药(Snowbreak Girl002/Girl002/Girl002_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1133,13 +1113,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002a_SkeletonData&amp;ui_show_data:1.193;0,0&amp;ui_show_idle_anim:sp_girl002a_gachastand</t>
@@ -1153,7 +1132,6 @@
           <t>尘白幻化药(Snowbreak Girl002/a/Girl002a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>1</t>
@@ -1181,13 +1159,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002a_01_q_SkeletonData&amp;ui_show_data:0.3687;0,0&amp;ui_show_idle_anim:sp_girl002a_01_q_stand</t>
@@ -1201,7 +1178,6 @@
           <t>尘白幻化药(Snowbreak Girl002/a_01_q/Girl002a_01_q_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
@@ -1229,13 +1205,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002a_02_SkeletonData&amp;ui_show_data:0.0758;0,0&amp;ui_show_idle_anim:sp_girl002a_02_gachastand</t>
@@ -1249,7 +1224,6 @@
           <t>尘白幻化药(Snowbreak Girl002/a_02/Girl002a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>1</t>
@@ -1277,13 +1251,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002a_03_SkeletonData&amp;ui_show_data:0.1636;0,0&amp;ui_show_idle_anim:sp_girl002a_03_gachastand</t>
@@ -1297,7 +1270,6 @@
           <t>尘白幻化药(Snowbreak Girl002/a_03/Girl002a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>1</t>
@@ -1325,13 +1297,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002b_SkeletonData&amp;ui_show_data:0.159;0,0&amp;ui_show_idle_anim:sp_girl002b_stand</t>
@@ -1345,7 +1316,6 @@
           <t>尘白幻化药(Snowbreak Girl002/b/Girl002b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>1</t>
@@ -1373,13 +1343,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>ui_show_res:Girl002b_02_SkeletonData&amp;ui_show_data:0.0982;0,0&amp;ui_show_idle_anim:sp_girl002b_02_gachastand</t>
@@ -1393,7 +1362,6 @@
           <t>尘白幻化药(Snowbreak Girl002/b_02/Girl002b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>1</t>
@@ -1421,13 +1389,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>ui_show_res:Girl003_01_SkeletonData&amp;ui_show_data:0.4657;0,0&amp;ui_show_idle_anim:sp_girl003_stand</t>
@@ -1441,7 +1408,6 @@
           <t>尘白幻化药(Snowbreak Girl003/01/Girl003_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>1</t>
@@ -1469,13 +1435,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>ui_show_res:Girl003_SkeletonData&amp;ui_show_data:0.25;0,0&amp;ui_show_idle_anim:sp_girl003_stand</t>
@@ -1489,7 +1454,6 @@
           <t>尘白幻化药(Snowbreak Girl003/Girl003/Girl003_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>1</t>
@@ -1517,13 +1481,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>ui_show_res:Girl003a_SkeletonData&amp;ui_show_data:0.1179;0,0&amp;ui_show_idle_anim:sp_girl003a_gachastand</t>
@@ -1537,7 +1500,6 @@
           <t>尘白幻化药(Snowbreak Girl003/a/Girl003a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>1</t>
@@ -1565,13 +1527,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>ui_show_res:Girl003a_02_SkeletonData&amp;ui_show_data:0.1407;0,0&amp;ui_show_idle_anim:sp_girl003a_02_gachastand</t>
@@ -1585,7 +1546,6 @@
           <t>尘白幻化药(Snowbreak Girl003/a_02/Girl003a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>1</t>
@@ -1613,13 +1573,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>ui_show_res:Girl003a_03_SkeletonData&amp;ui_show_data:0.0939;0,0&amp;ui_show_idle_anim:sp_girl003a_03_gachastand</t>
@@ -1633,7 +1592,6 @@
           <t>尘白幻化药(Snowbreak Girl003/a_03/Girl003a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>1</t>
@@ -1661,13 +1619,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>ui_show_res:Girl004_01_SkeletonData&amp;ui_show_data:0.2516;0,0&amp;ui_show_idle_anim:sp_girl004_stand</t>
@@ -1681,7 +1638,6 @@
           <t>尘白幻化药(Snowbreak Girl004/01/Girl004_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>1</t>
@@ -1709,13 +1665,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>ui_show_res:Girl004_02_SkeletonData&amp;ui_show_data:0.2516;0,0&amp;ui_show_idle_anim:sp_girl004_stand</t>
@@ -1729,7 +1684,6 @@
           <t>尘白幻化药(Snowbreak Girl004/02/Girl004_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>1</t>
@@ -1757,13 +1711,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>ui_show_res:Girl004_SkeletonData&amp;ui_show_data:0.2498;0,0&amp;ui_show_idle_anim:sp_girl004_stand</t>
@@ -1777,7 +1730,6 @@
           <t>尘白幻化药(Snowbreak Girl004/Girl004/Girl004_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>1</t>
@@ -1805,13 +1757,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>ui_show_res:girl004a_02_SkeletonData&amp;ui_show_data:0.1002;0,0&amp;ui_show_idle_anim:sp_girl004a_02_gachastand</t>
@@ -1825,7 +1776,6 @@
           <t>尘白幻化药(Snowbreak Girl004/a_02/girl004a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>1</t>
@@ -1853,13 +1803,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>ui_show_res:girl004a_03_SkeletonData&amp;ui_show_data:0.4921;0,0&amp;ui_show_idle_anim:sp_girl004a_03_gachastand</t>
@@ -1873,7 +1822,6 @@
           <t>尘白幻化药(Snowbreak Girl004/a_03/girl004a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>1</t>
@@ -1901,13 +1849,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>ui_show_res:Girl004b_SkeletonData&amp;ui_show_data:0.2378;0,0&amp;ui_show_idle_anim:sp_girl004_stand</t>
@@ -1921,7 +1868,6 @@
           <t>尘白幻化药(Snowbreak Girl004/b/Girl004b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>1</t>
@@ -1949,13 +1895,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>ui_show_res:Girl004b_02_SkeletonData&amp;ui_show_data:0.1117;0,0&amp;ui_show_idle_anim:sp_girl004b_02_stand</t>
@@ -1969,7 +1914,6 @@
           <t>尘白幻化药(Snowbreak Girl004/b_02/Girl004b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>1</t>
@@ -1997,13 +1941,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>ui_show_res:Girl004b_04_SkeletonData&amp;ui_show_data:0.0878;0,0&amp;ui_show_idle_anim:sp_girl004b_04_gachastand</t>
@@ -2017,7 +1960,6 @@
           <t>尘白幻化药(Snowbreak Girl004/b_04/Girl004b_04_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>1</t>
@@ -2045,13 +1987,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005_01_SkeletonData&amp;ui_show_data:0.2252;0,0&amp;ui_show_idle_anim:sp_girl005_01_stand</t>
@@ -2065,7 +2006,6 @@
           <t>尘白幻化药(Snowbreak Girl005/01/Girl005_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>1</t>
@@ -2093,13 +2033,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005_SkeletonData&amp;ui_show_data:0.2264;0,0&amp;ui_show_idle_anim:sp_girl005_stand</t>
@@ -2113,7 +2052,6 @@
           <t>尘白幻化药(Snowbreak Girl005/Girl005/Girl005_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>1</t>
@@ -2141,13 +2079,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005a_SkeletonData&amp;ui_show_data:0.2254;0,0&amp;ui_show_idle_anim:sp_girl005_stand</t>
@@ -2161,7 +2098,6 @@
           <t>尘白幻化药(Snowbreak Girl005/a/Girl005a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>1</t>
@@ -2189,13 +2125,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005a_01_q_SkeletonData&amp;ui_show_data:0.363;0,0&amp;ui_show_idle_anim:sp_girl005a_01_q_stand</t>
@@ -2209,7 +2144,6 @@
           <t>尘白幻化药(Snowbreak Girl005/a_01_q/Girl005a_01_q_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>1</t>
@@ -2237,13 +2171,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005a_03_SkeletonData&amp;ui_show_data:0.133;0,0&amp;ui_show_idle_anim:sp_girl005a_03_gachastand</t>
@@ -2257,7 +2190,6 @@
           <t>尘白幻化药(Snowbreak Girl005/a_03/Girl005a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>1</t>
@@ -2285,13 +2217,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005b_SkeletonData&amp;ui_show_data:0.1107;0,0&amp;ui_show_idle_anim:sp_girl005b_gacha_stand</t>
@@ -2305,7 +2236,6 @@
           <t>尘白幻化药(Snowbreak Girl005/b/Girl005b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>1</t>
@@ -2333,13 +2263,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005b_02_SkeletonData&amp;ui_show_data:0.2192;0,0&amp;ui_show_idle_anim:sp_girl005_stand</t>
@@ -2353,7 +2282,6 @@
           <t>尘白幻化药(Snowbreak Girl005/b_02/Girl005b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>1</t>
@@ -2381,13 +2309,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005b_03_SkeletonData&amp;ui_show_data:0.1868;0,0&amp;ui_show_idle_anim:sp_girl005b_03_gachastand</t>
@@ -2401,7 +2328,6 @@
           <t>尘白幻化药(Snowbreak Girl005/b_03/Girl005b_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>1</t>
@@ -2429,13 +2355,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005c_SkeletonData&amp;ui_show_data:0.1136;0,0&amp;ui_show_idle_anim:sp_girl005c_gachastand</t>
@@ -2449,7 +2374,6 @@
           <t>尘白幻化药(Snowbreak Girl005/c/Girl005c_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>1</t>
@@ -2477,13 +2401,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>ui_show_res:Girl005c_02_SkeletonData&amp;ui_show_data:0.0908;0,0&amp;ui_show_idle_anim:sp_girl005c_02_gachastand</t>
@@ -2497,7 +2420,6 @@
           <t>尘白幻化药(Snowbreak Girl005/c_02/Girl005c_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>1</t>
@@ -2525,13 +2447,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>ui_show_res:Girl006_01_SkeletonData&amp;ui_show_data:0.2296;0,0&amp;ui_show_idle_anim:sp_girl006_stand</t>
@@ -2545,7 +2466,6 @@
           <t>尘白幻化药(Snowbreak Girl006/01/Girl006_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>1</t>
@@ -2573,13 +2493,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>ui_show_res:Girl006_SkeletonData&amp;ui_show_data:0.2288;0,0&amp;ui_show_idle_anim:sp_girl006_stand</t>
@@ -2593,7 +2512,6 @@
           <t>尘白幻化药(Snowbreak Girl006/Girl006/Girl006_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>1</t>
@@ -2621,13 +2539,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>ui_show_res:Girl006b_SkeletonData&amp;ui_show_data:0.1404;0,0&amp;ui_show_idle_anim:sp_girl006b_gachastand</t>
@@ -2641,7 +2558,6 @@
           <t>尘白幻化药(Snowbreak Girl006/b/Girl006b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>1</t>
@@ -2669,13 +2585,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>ui_show_res:Girl006b_02_SkeletonData&amp;ui_show_data:0.1354;0,0&amp;ui_show_idle_anim:sp_girl006b_02_gachastand</t>
@@ -2689,7 +2604,6 @@
           <t>尘白幻化药(Snowbreak Girl006/b_02/Girl006b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>1</t>
@@ -2717,13 +2631,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007_01_SkeletonData&amp;ui_show_data:0.2264;0,0&amp;ui_show_idle_anim:sp_girl007_01_stand</t>
@@ -2737,7 +2650,6 @@
           <t>尘白幻化药(Snowbreak Girl007/01/Girl007_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>1</t>
@@ -2765,13 +2677,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007_02_SkeletonData&amp;ui_show_data:0.2287;0,0&amp;ui_show_idle_anim:sp_girl007_00_stand</t>
@@ -2785,7 +2696,6 @@
           <t>尘白幻化药(Snowbreak Girl007/02/Girl007_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>1</t>
@@ -2813,13 +2723,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007_SkeletonData&amp;ui_show_data:0.2285;0,0&amp;ui_show_idle_anim:sp_girl007_00_stand</t>
@@ -2833,7 +2742,6 @@
           <t>尘白幻化药(Snowbreak Girl007/Girl007/Girl007_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>1</t>
@@ -2861,13 +2769,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007a_SkeletonData&amp;ui_show_data:0.0889;0,0&amp;ui_show_idle_anim:sp_girl007a_gachastand</t>
@@ -2881,7 +2788,6 @@
           <t>尘白幻化药(Snowbreak Girl007/a/Girl007a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>1</t>
@@ -2909,13 +2815,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007a_02_SkeletonData&amp;ui_show_data:0.1093;0,0&amp;ui_show_idle_anim:sp_girl007a_02_gachastand</t>
@@ -2929,7 +2834,6 @@
           <t>尘白幻化药(Snowbreak Girl007/a_02/Girl007a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>1</t>
@@ -2957,13 +2861,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007a_03_SkeletonData&amp;ui_show_data:0.2333;0,0&amp;ui_show_idle_anim:sp_girl007_03_stand</t>
@@ -2977,7 +2880,6 @@
           <t>尘白幻化药(Snowbreak Girl007/a_03/Girl007a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>1</t>
@@ -3005,13 +2907,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007a_04_SkeletonData&amp;ui_show_data:0.2387;0,0&amp;ui_show_idle_anim:sp_girl007_00_stand</t>
@@ -3025,7 +2926,6 @@
           <t>尘白幻化药(Snowbreak Girl007/a_04/Girl007a_04_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>1</t>
@@ -3053,13 +2953,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>ui_show_res:Girl007a_05_SkeletonData&amp;ui_show_data:0.1438;0,0&amp;ui_show_idle_anim:sp_girl007a_05_gachastand</t>
@@ -3073,7 +2972,6 @@
           <t>尘白幻化药(Snowbreak Girl007/a_05/Girl007a_05_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>1</t>
@@ -3101,13 +2999,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008_01_SkeletonData&amp;ui_show_data:0.2438;0,0&amp;ui_show_idle_anim:sp_girl008_stand</t>
@@ -3121,7 +3018,6 @@
           <t>尘白幻化药(Snowbreak Girl008/01/Girl008_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>1</t>
@@ -3149,13 +3045,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008_02_SkeletonData&amp;ui_show_data:0.2442;0,0&amp;ui_show_idle_anim:sp_girl008_stand</t>
@@ -3169,7 +3064,6 @@
           <t>尘白幻化药(Snowbreak Girl008/02/Girl008_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>1</t>
@@ -3197,13 +3091,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008_SkeletonData&amp;ui_show_data:0.4835;0,0&amp;ui_show_idle_anim:sp_girl008_stand</t>
@@ -3217,7 +3110,6 @@
           <t>尘白幻化药(Snowbreak Girl008/Girl008/Girl008_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>1</t>
@@ -3245,13 +3137,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008a_01_q_SkeletonData&amp;ui_show_data:0.3672;0,0&amp;ui_show_idle_anim:sp_girl008a_01_q_stand</t>
@@ -3265,7 +3156,6 @@
           <t>尘白幻化药(Snowbreak Girl008/a_01_q/Girl008a_01_q_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>1</t>
@@ -3293,13 +3183,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008a_03_SkeletonData&amp;ui_show_data:0.1438;0,0&amp;ui_show_idle_anim:sp_girl008a_03_gachastand</t>
@@ -3313,7 +3202,6 @@
           <t>尘白幻化药(Snowbreak Girl008/a_03/Girl008a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>1</t>
@@ -3341,13 +3229,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008a_04_SkeletonData&amp;ui_show_data:0.1197;0,0&amp;ui_show_idle_anim:sp_girl008a_04_gachastand</t>
@@ -3361,7 +3248,6 @@
           <t>尘白幻化药(Snowbreak Girl008/a_04/Girl008a_04_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>1</t>
@@ -3389,13 +3275,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008b_SkeletonData&amp;ui_show_data:0.2493;0,0&amp;ui_show_idle_anim:sp_girl008_stand</t>
@@ -3409,7 +3294,6 @@
           <t>尘白幻化药(Snowbreak Girl008/b/Girl008b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>1</t>
@@ -3437,13 +3321,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008b_02_SkeletonData&amp;ui_show_data:0.2211;0,0&amp;ui_show_idle_anim:sp_girl008b_02_stand</t>
@@ -3457,7 +3340,6 @@
           <t>尘白幻化药(Snowbreak Girl008/b_02/Girl008b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>1</t>
@@ -3485,13 +3367,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008b_03_SkeletonData&amp;ui_show_data:0.1474;0,0&amp;ui_show_idle_anim:sp_girl008b_03_gachastand</t>
@@ -3505,7 +3386,6 @@
           <t>尘白幻化药(Snowbreak Girl008/b_03/Girl008b_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>1</t>
@@ -3533,13 +3413,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008c_SkeletonData&amp;ui_show_data:0.1022;0,0&amp;ui_show_idle_anim:sp_girl008c_gachastand</t>
@@ -3553,7 +3432,6 @@
           <t>尘白幻化药(Snowbreak Girl008/c/Girl008c_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>1</t>
@@ -3581,13 +3459,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008c_02_SkeletonData&amp;ui_show_data:0.0883;0,0&amp;ui_show_idle_anim:sp_girl008c_02_gachastand</t>
@@ -3601,7 +3478,6 @@
           <t>尘白幻化药(Snowbreak Girl008/c_02/Girl008c_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>1</t>
@@ -3629,13 +3505,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>ui_show_res:Girl008c_03_SkeletonData&amp;ui_show_data:0.1405;0,0&amp;ui_show_idle_anim:sp_girl008c_03_gachastand</t>
@@ -3649,7 +3524,6 @@
           <t>尘白幻化药(Snowbreak Girl008/c_03/Girl008c_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>1</t>
@@ -3677,13 +3551,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010_01_SkeletonData&amp;ui_show_data:0.2289;0,0&amp;ui_show_idle_anim:sp_girl010_stand</t>
@@ -3697,7 +3570,6 @@
           <t>尘白幻化药(Snowbreak Girl010/01/Girl010_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>1</t>
@@ -3725,13 +3597,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010_SkeletonData&amp;ui_show_data:0.2282;0,0&amp;ui_show_idle_anim:sp_girl010_stand</t>
@@ -3745,7 +3616,6 @@
           <t>尘白幻化药(Snowbreak Girl010/Girl010/Girl010_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>1</t>
@@ -3773,13 +3643,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010a_SkeletonData&amp;ui_show_data:0.1539;0,0&amp;ui_show_idle_anim:sp_girl010a_gachastand</t>
@@ -3793,7 +3662,6 @@
           <t>尘白幻化药(Snowbreak Girl010/a/Girl010a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>1</t>
@@ -3821,13 +3689,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010a_03_SkeletonData&amp;ui_show_data:0.0961;0,0&amp;ui_show_idle_anim:sp_girl010a_03_gachastand</t>
@@ -3841,7 +3708,6 @@
           <t>尘白幻化药(Snowbreak Girl010/a_03/Girl010a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>1</t>
@@ -3869,13 +3735,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010a_04_SkeletonData&amp;ui_show_data:0.2224;0,0&amp;ui_show_idle_anim:sp_girl010a_04_gachastand_01</t>
@@ -3889,7 +3754,6 @@
           <t>尘白幻化药(Snowbreak Girl010/a_04/Girl010a_04_SkeletonData.asset stand链:含stand)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>1</t>
@@ -3917,13 +3781,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010b_SkeletonData&amp;ui_show_data:0.1304;0,0&amp;ui_show_idle_anim:sp_girl010b_gacha_stand</t>
@@ -3937,7 +3800,6 @@
           <t>尘白幻化药(Snowbreak Girl010/b/Girl010b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>1</t>
@@ -3965,13 +3827,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010b_02_SkeletonData&amp;ui_show_data:0.1163;0,0&amp;ui_show_idle_anim:sp_girl010b_02_gacha_stand</t>
@@ -3985,7 +3846,6 @@
           <t>尘白幻化药(Snowbreak Girl010/b_02/Girl010b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>1</t>
@@ -4013,13 +3873,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>ui_show_res:Girl010b_03_SkeletonData&amp;ui_show_data:0.1437;0,0&amp;ui_show_idle_anim:sp_girl010b_03_gachastand</t>
@@ -4033,7 +3892,6 @@
           <t>尘白幻化药(Snowbreak Girl010/b_03/Girl010b_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>1</t>
@@ -4061,13 +3919,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011_01_SkeletonData&amp;ui_show_data:0.228;0,0&amp;ui_show_idle_anim:sp_girl011_stand</t>
@@ -4081,7 +3938,6 @@
           <t>尘白幻化药(Snowbreak Girl011/01/Girl011_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>1</t>
@@ -4109,13 +3965,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011_02_SkeletonData&amp;ui_show_data:0.1107;0,0&amp;ui_show_idle_anim:sp_girl011_02_gachastand</t>
@@ -4129,7 +3984,6 @@
           <t>尘白幻化药(Snowbreak Girl011/02/Girl011_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>1</t>
@@ -4157,13 +4011,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011_SkeletonData&amp;ui_show_data:0.2228;0,0&amp;ui_show_idle_anim:sp_girl011_stand</t>
@@ -4177,7 +4030,6 @@
           <t>尘白幻化药(Snowbreak Girl011/Girl011/Girl011_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>1</t>
@@ -4205,13 +4057,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011a_SkeletonData&amp;ui_show_data:0.1938;0,0&amp;ui_show_idle_anim:sp_girl011a_gachastand</t>
@@ -4225,7 +4076,6 @@
           <t>尘白幻化药(Snowbreak Girl011/a/Girl011a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>1</t>
@@ -4253,13 +4103,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011a_02_SkeletonData&amp;ui_show_data:0.0806;0,0&amp;ui_show_idle_anim:sp_girl011a_02_gachastand</t>
@@ -4273,7 +4122,6 @@
           <t>尘白幻化药(Snowbreak Girl011/a_02/Girl011a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>1</t>
@@ -4301,13 +4149,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011a_03_SkeletonData&amp;ui_show_data:0.0997;0,0&amp;ui_show_idle_anim:sp_girl011a_03_gachaidle</t>
@@ -4321,7 +4168,6 @@
           <t>尘白幻化药(Snowbreak Girl011/a_03/Girl011a_03_SkeletonData.asset stand链:含idle)</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>1</t>
@@ -4349,13 +4195,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011b_SkeletonData&amp;ui_show_data:0.1083;0,0&amp;ui_show_idle_anim:sp_girl011b_gachastand</t>
@@ -4369,7 +4214,6 @@
           <t>尘白幻化药(Snowbreak Girl011/b/Girl011b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>1</t>
@@ -4397,13 +4241,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011b_02_SkeletonData&amp;ui_show_data:0.0977;0,0&amp;ui_show_idle_anim:sp_girl011b_02_gachastand</t>
@@ -4417,7 +4260,6 @@
           <t>尘白幻化药(Snowbreak Girl011/b_02/Girl011b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>1</t>
@@ -4445,13 +4287,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>ui_show_res:Girl011b_03_SkeletonData&amp;ui_show_data:0.1406;0,0&amp;ui_show_idle_anim:sp_girl011b_03_gachastand</t>
@@ -4465,7 +4306,6 @@
           <t>尘白幻化药(Snowbreak Girl011/b_03/Girl011b_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>1</t>
@@ -4493,13 +4333,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>ui_show_res:Girl012_01_SkeletonData&amp;ui_show_data:0.2103;0,0&amp;ui_show_idle_anim:sp_girl012_stand</t>
@@ -4513,7 +4352,6 @@
           <t>尘白幻化药(Snowbreak Girl012/01/Girl012_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>1</t>
@@ -4541,13 +4379,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>ui_show_res:Girl012_SkeletonData&amp;ui_show_data:0.2103;0,0&amp;ui_show_idle_anim:sp_girl012_stand</t>
@@ -4561,7 +4398,6 @@
           <t>尘白幻化药(Snowbreak Girl012/Girl012/Girl012_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>1</t>
@@ -4589,13 +4425,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>ui_show_res:Girl012a_SkeletonData&amp;ui_show_data:0.1169;0,0&amp;ui_show_idle_anim:sp_girl012a_gachastand</t>
@@ -4609,7 +4444,6 @@
           <t>尘白幻化药(Snowbreak Girl012/a/Girl012a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>1</t>
@@ -4637,13 +4471,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>ui_show_res:Girl012a_02_SkeletonData&amp;ui_show_data:0.1039;0,0&amp;ui_show_idle_anim:sp_girl012a_02_gachastand</t>
@@ -4657,7 +4490,6 @@
           <t>尘白幻化药(Snowbreak Girl012/a_02/Girl012a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>1</t>
@@ -4685,13 +4517,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>ui_show_res:Girl012b_SkeletonData&amp;ui_show_data:0.0882;0,0&amp;ui_show_idle_anim:sp_girl012b_gachastand</t>
@@ -4705,7 +4536,6 @@
           <t>尘白幻化药(Snowbreak Girl012/b/Girl012b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>1</t>
@@ -4733,13 +4563,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>ui_show_res:Girl012b_02_SkeletonData&amp;ui_show_data:0.0774;0,0&amp;ui_show_idle_anim:sp_girl012b_02_gachastand</t>
@@ -4753,7 +4582,6 @@
           <t>尘白幻化药(Snowbreak Girl012/b_02/Girl012b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>1</t>
@@ -4781,13 +4609,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013_01_SkeletonData&amp;ui_show_data:0.2353;0,0&amp;ui_show_idle_anim:sp_girl013_stand</t>
@@ -4801,7 +4628,6 @@
           <t>尘白幻化药(Snowbreak Girl013/01/Girl013_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>1</t>
@@ -4829,13 +4655,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013_02_SkeletonData&amp;ui_show_data:0.2352;0,0&amp;ui_show_idle_anim:sp_girl013_stand</t>
@@ -4849,7 +4674,6 @@
           <t>尘白幻化药(Snowbreak Girl013/02/Girl013_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>1</t>
@@ -4877,13 +4701,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013_SkeletonData&amp;ui_show_data:0.2012;0,0&amp;ui_show_idle_anim:sp_girl013_stand</t>
@@ -4897,7 +4720,6 @@
           <t>尘白幻化药(Snowbreak Girl013/Girl013/Girl013_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>1</t>
@@ -4925,13 +4747,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013a_SkeletonData&amp;ui_show_data:0.2529;0,0&amp;ui_show_idle_anim:sp_girl013_stand</t>
@@ -4945,7 +4766,6 @@
           <t>尘白幻化药(Snowbreak Girl013/a/Girl013a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>1</t>
@@ -4973,13 +4793,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013a_02_SkeletonData&amp;ui_show_data:0.1439;0,0&amp;ui_show_idle_anim:girl013a_02stand</t>
@@ -4993,7 +4812,6 @@
           <t>尘白幻化药(Snowbreak Girl013/a_02/Girl013a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>1</t>
@@ -5021,13 +4839,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013a_04_SkeletonData&amp;ui_show_data:0.0716;0,0&amp;ui_show_idle_anim:sp_girl013a_04_gacha_stand</t>
@@ -5041,7 +4858,6 @@
           <t>尘白幻化药(Snowbreak Girl013/a_04/Girl013a_04_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>1</t>
@@ -5069,13 +4885,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013b_SkeletonData&amp;ui_show_data:0.1085;0,0&amp;ui_show_idle_anim:sp_girl013b_gachastand</t>
@@ -5089,7 +4904,6 @@
           <t>尘白幻化药(Snowbreak Girl013/b/Girl013b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>1</t>
@@ -5117,13 +4931,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013b_02_SkeletonData&amp;ui_show_data:0.1086;0,0&amp;ui_show_idle_anim:sp_girl013b_02_gachastand</t>
@@ -5137,7 +4950,6 @@
           <t>尘白幻化药(Snowbreak Girl013/b_02/Girl013b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>1</t>
@@ -5165,13 +4977,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>ui_show_res:Girl013b_03_SkeletonData&amp;ui_show_data:0.0997;0,0&amp;ui_show_idle_anim:sp_girl013b_03_gachastand</t>
@@ -5185,7 +4996,6 @@
           <t>尘白幻化药(Snowbreak Girl013/b_03/Girl013b_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>1</t>
@@ -5213,13 +5023,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014_01_SkeletonData&amp;ui_show_data:0.2136;0,0&amp;ui_show_idle_anim:sp_girl014_stand</t>
@@ -5233,7 +5042,6 @@
           <t>尘白幻化药(Snowbreak Girl014/01/Girl014_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>1</t>
@@ -5261,13 +5069,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014_SkeletonData&amp;ui_show_data:0.1782;0,0&amp;ui_show_idle_anim:sp_girl014_stand</t>
@@ -5281,7 +5088,6 @@
           <t>尘白幻化药(Snowbreak Girl014/Girl014/Girl014_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>1</t>
@@ -5309,13 +5115,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014a_SkeletonData&amp;ui_show_data:0.1816;0,0&amp;ui_show_idle_anim:sp_girl014a_gachastand</t>
@@ -5329,7 +5134,6 @@
           <t>尘白幻化药(Snowbreak Girl014/a/Girl014a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>1</t>
@@ -5357,13 +5161,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014a_03_SkeletonData&amp;ui_show_data:0.2127;0,0&amp;ui_show_idle_anim:sp_girl014_stand</t>
@@ -5377,7 +5180,6 @@
           <t>尘白幻化药(Snowbreak Girl014/a_03/Girl014a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>1</t>
@@ -5405,13 +5207,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014a_04_SkeletonData&amp;ui_show_data:0.109;0,0&amp;ui_show_idle_anim:sp_girl014a_04_gachaidle</t>
@@ -5425,7 +5226,6 @@
           <t>尘白幻化药(Snowbreak Girl014/a_04/Girl014a_04_SkeletonData.asset stand链:含idle)</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>1</t>
@@ -5453,13 +5253,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014b_SkeletonData&amp;ui_show_data:0.1432;0,0&amp;ui_show_idle_anim:sp_girl014b_stand</t>
@@ -5473,7 +5272,6 @@
           <t>尘白幻化药(Snowbreak Girl014/b/Girl014b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>1</t>
@@ -5501,13 +5299,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014b_02_SkeletonData&amp;ui_show_data:0.1078;0,0&amp;ui_show_idle_anim:sp_girl014b_02_gacha_stand</t>
@@ -5521,7 +5318,6 @@
           <t>尘白幻化药(Snowbreak Girl014/b_02/Girl014b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>1</t>
@@ -5549,13 +5345,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>ui_show_res:Girl014b_03_SkeletonData&amp;ui_show_data:0.1361;0,0&amp;ui_show_idle_anim:sp_girl014b_03_gachastand</t>
@@ -5569,7 +5364,6 @@
           <t>尘白幻化药(Snowbreak Girl014/b_03/Girl014b_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>1</t>
@@ -5597,13 +5391,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H107" t="n">
         <v>0</v>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015_01_SkeletonData&amp;ui_show_data:0.2277;0,0&amp;ui_show_idle_anim:sp_girl015_stand</t>
@@ -5617,7 +5410,6 @@
           <t>尘白幻化药(Snowbreak Girl015/01/Girl015_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>1</t>
@@ -5645,13 +5437,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015_02_SkeletonData&amp;ui_show_data:0.1401;0,0&amp;ui_show_idle_anim:sp_girl015_02_gachastand</t>
@@ -5665,7 +5456,6 @@
           <t>尘白幻化药(Snowbreak Girl015/02/Girl015_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>1</t>
@@ -5693,13 +5483,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015_04_SkeletonData&amp;ui_show_data:0.0921;0,0&amp;ui_show_idle_anim:sp_girl015_04_01_gachastand</t>
@@ -5713,7 +5502,6 @@
           <t>尘白幻化药(Snowbreak Girl015/04/Girl015_04_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>1</t>
@@ -5741,13 +5529,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H110" t="n">
         <v>0</v>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015_SkeletonData&amp;ui_show_data:0.155;0,0&amp;ui_show_idle_anim:sp_girl015_gachastand</t>
@@ -5761,7 +5548,6 @@
           <t>尘白幻化药(Snowbreak Girl015/Girl015/Girl015_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>1</t>
@@ -5789,13 +5575,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015a_SkeletonData&amp;ui_show_data:0.1113;0,0&amp;ui_show_idle_anim:sp_girl015a_gacha</t>
@@ -5809,7 +5594,6 @@
           <t>尘白幻化药(Snowbreak Girl015/a/Girl015a_SkeletonData.asset stand链:首个动画兜底)</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>1</t>
@@ -5837,13 +5621,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015a_02_SkeletonData&amp;ui_show_data:0.2071;0,0&amp;ui_show_idle_anim:sp_girl015_stand</t>
@@ -5857,7 +5640,6 @@
           <t>尘白幻化药(Snowbreak Girl015/a_02/Girl015a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>1</t>
@@ -5885,13 +5667,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015a_04_SkeletonData&amp;ui_show_data:0.1613;0,0&amp;ui_show_idle_anim:sp_girl015a_04_gachastand</t>
@@ -5905,7 +5686,6 @@
           <t>尘白幻化药(Snowbreak Girl015/a_04/Girl015a_04_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>1</t>
@@ -5933,13 +5713,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H114" t="n">
         <v>0</v>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015b_SkeletonData&amp;ui_show_data:0.1018;0,0&amp;ui_show_idle_anim:sp_girl015b_gachastand</t>
@@ -5953,7 +5732,6 @@
           <t>尘白幻化药(Snowbreak Girl015/b/Girl015b_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>1</t>
@@ -5981,13 +5759,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015b_02_SkeletonData&amp;ui_show_data:0.1338;0,0&amp;ui_show_idle_anim:sp_girl015b_02_gachastand</t>
@@ -6001,7 +5778,6 @@
           <t>尘白幻化药(Snowbreak Girl015/b_02/Girl015b_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>1</t>
@@ -6029,13 +5805,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>ui_show_res:Girl015b_03_SkeletonData&amp;ui_show_data:0.1101;0,0&amp;ui_show_idle_anim:sp_girl015b_03_gachastand</t>
@@ -6049,7 +5824,6 @@
           <t>尘白幻化药(Snowbreak Girl015/b_03/Girl015b_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>1</t>
@@ -6077,13 +5851,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>ui_show_res:Girl016_01_SkeletonData&amp;ui_show_data:0.2436;0,0&amp;ui_show_idle_anim:sp_girl016_stand</t>
@@ -6097,7 +5870,6 @@
           <t>尘白幻化药(Snowbreak Girl016/01/Girl016_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>1</t>
@@ -6125,13 +5897,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>ui_show_res:Girl016_02_SkeletonData&amp;ui_show_data:0.1183;0,0&amp;ui_show_idle_anim:sp_girl016_02_gachastand</t>
@@ -6145,7 +5916,6 @@
           <t>尘白幻化药(Snowbreak Girl016/02/Girl016_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>1</t>
@@ -6173,13 +5943,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>ui_show_res:Girl016_03_SkeletonData&amp;ui_show_data:0.2087;0,0&amp;ui_show_idle_anim:sp_girl016_stand</t>
@@ -6193,7 +5962,6 @@
           <t>尘白幻化药(Snowbreak Girl016/03/Girl016_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>1</t>
@@ -6221,13 +5989,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>ui_show_res:Girl016_04_SkeletonData&amp;ui_show_data:0.0979;0,0&amp;ui_show_idle_anim:sp_girl016_04_gachastand</t>
@@ -6241,7 +6008,6 @@
           <t>尘白幻化药(Snowbreak Girl016/04/Girl016_04_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>1</t>
@@ -6269,13 +6035,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>ui_show_res:Girl016_SkeletonData&amp;ui_show_data:0.0636;0,0&amp;ui_show_idle_anim:sp_girl016_gachastand</t>
@@ -6289,7 +6054,6 @@
           <t>尘白幻化药(Snowbreak Girl016/Girl016/Girl016_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>1</t>
@@ -6317,13 +6081,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>ui_show_res:Girl017_01_SkeletonData&amp;ui_show_data:0.2374;0,0&amp;ui_show_idle_anim:sp_girl017_stand</t>
@@ -6337,7 +6100,6 @@
           <t>尘白幻化药(Snowbreak Girl017/01/Girl017_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>1</t>
@@ -6365,13 +6127,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>ui_show_res:Girl017_02_SkeletonData&amp;ui_show_data:0.1299;0,0&amp;ui_show_idle_anim:sp_girl017_02_stand</t>
@@ -6385,7 +6146,6 @@
           <t>尘白幻化药(Snowbreak Girl017/02/Girl017_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
           <t>1</t>
@@ -6413,13 +6173,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>ui_show_res:Girl017_03_SkeletonData&amp;ui_show_data:0.2377;0,0&amp;ui_show_idle_anim:sp_girl017_stand</t>
@@ -6433,7 +6192,6 @@
           <t>尘白幻化药(Snowbreak Girl017/03/Girl017_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>1</t>
@@ -6461,13 +6219,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H125" t="n">
         <v>0</v>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>ui_show_res:Girl017_SkeletonData&amp;ui_show_data:0.188;0,0&amp;ui_show_idle_anim:sp_girl017_gachastand</t>
@@ -6481,7 +6238,6 @@
           <t>尘白幻化药(Snowbreak Girl017/Girl017/Girl017_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>1</t>
@@ -6509,13 +6265,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>ui_show_res:Girl017a_SkeletonData&amp;ui_show_data:0.103;0,0&amp;ui_show_idle_anim:sp_girl017a_gachastand</t>
@@ -6529,7 +6284,6 @@
           <t>尘白幻化药(Snowbreak Girl017/a/Girl017a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>1</t>
@@ -6557,13 +6311,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>ui_show_res:Girl017a_02_SkeletonData&amp;ui_show_data:0.0936;0,0&amp;ui_show_idle_anim:sp_girl017a_02_gachastand_a</t>
@@ -6577,7 +6330,6 @@
           <t>尘白幻化药(Snowbreak Girl017/a_02/Girl017a_02_SkeletonData.asset stand链:含stand)</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>1</t>
@@ -6605,13 +6357,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>ui_show_res:Girl018_01_SkeletonData&amp;ui_show_data:0.2182;0,0&amp;ui_show_idle_anim:sp_girl018_stand</t>
@@ -6625,7 +6376,6 @@
           <t>尘白幻化药(Snowbreak Girl018/01/Girl018_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>1</t>
@@ -6653,13 +6403,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>ui_show_res:Girl018_02_SkeletonData&amp;ui_show_data:0.1217;0,0&amp;ui_show_idle_anim:sp_girl018_02_gachastand</t>
@@ -6673,7 +6422,6 @@
           <t>尘白幻化药(Snowbreak Girl018/02/Girl018_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>1</t>
@@ -6701,13 +6449,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>ui_show_res:Girl018_03_SkeletonData&amp;ui_show_data:0.0717;0,0&amp;ui_show_idle_anim:sp_girl018_03_gachastand</t>
@@ -6721,7 +6468,6 @@
           <t>尘白幻化药(Snowbreak Girl018/03/Girl018_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>1</t>
@@ -6749,13 +6495,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>ui_show_res:Girl018_SkeletonData&amp;ui_show_data:0.1053;0,0&amp;ui_show_idle_anim:sp_girl018_gacha_stand</t>
@@ -6769,7 +6514,6 @@
           <t>尘白幻化药(Snowbreak Girl018/Girl018/Girl018_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
           <t>1</t>
@@ -6797,13 +6541,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>ui_show_res:Girl018a_SkeletonData&amp;ui_show_data:0.1182;0,0&amp;ui_show_idle_anim:sp_girl018a_gachastand</t>
@@ -6817,7 +6560,6 @@
           <t>尘白幻化药(Snowbreak Girl018/a/Girl018a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr">
         <is>
           <t>1</t>
@@ -6845,13 +6587,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H133" t="n">
         <v>0</v>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>ui_show_res:Girl018a_02_SkeletonData&amp;ui_show_data:0.1495;0,0&amp;ui_show_idle_anim:sp_girl018a_02_gachastand</t>
@@ -6865,7 +6606,6 @@
           <t>尘白幻化药(Snowbreak Girl018/a_02/Girl018a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>1</t>
@@ -6893,13 +6633,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>ui_show_res:Girl018a_03_SkeletonData&amp;ui_show_data:0.0921;0,0&amp;ui_show_idle_anim:sp_girl018a_03_gachastand</t>
@@ -6913,7 +6652,6 @@
           <t>尘白幻化药(Snowbreak Girl018/a_03/Girl018a_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr">
         <is>
           <t>1</t>
@@ -6941,13 +6679,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H135" t="n">
         <v>0</v>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>ui_show_res:Girl020_01_SkeletonData&amp;ui_show_data:0.3086;0,0&amp;ui_show_idle_anim:sp_girl020_stand</t>
@@ -6961,7 +6698,6 @@
           <t>尘白幻化药(Snowbreak Girl020/01/Girl020_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr">
         <is>
           <t>1</t>
@@ -6989,13 +6725,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H136" t="n">
         <v>0</v>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>ui_show_res:Girl020_02_SkeletonData&amp;ui_show_data:0.0827;0,0&amp;ui_show_idle_anim:sp_girl020_02_gachastand</t>
@@ -7009,7 +6744,6 @@
           <t>尘白幻化药(Snowbreak Girl020/02/Girl020_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>1</t>
@@ -7037,13 +6771,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>ui_show_res:Girl020_03_SkeletonData&amp;ui_show_data:0.1572;0,0&amp;ui_show_idle_anim:sp_girl020_03_gachastand</t>
@@ -7057,7 +6790,6 @@
           <t>尘白幻化药(Snowbreak Girl020/03/Girl020_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
           <t>1</t>
@@ -7085,13 +6817,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H138" t="n">
         <v>0</v>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>ui_show_res:Girl020_SkeletonData&amp;ui_show_data:0.1017;0,0&amp;ui_show_idle_anim:sp_girl020_gacha_stand</t>
@@ -7105,7 +6836,6 @@
           <t>尘白幻化药(Snowbreak Girl020/Girl020/Girl020_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>1</t>
@@ -7133,13 +6863,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>ui_show_res:Girl020a_SkeletonData&amp;ui_show_data:0.0934;0,0&amp;ui_show_idle_anim:sp_girl020a_gachastand</t>
@@ -7153,7 +6882,6 @@
           <t>尘白幻化药(Snowbreak Girl020/a/Girl020a_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>1</t>
@@ -7181,13 +6909,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H140" t="n">
         <v>0</v>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>ui_show_res:Girl020a_02_SkeletonData&amp;ui_show_data:0.098;0,0&amp;ui_show_idle_anim:sp_girl020a_02_gachastand</t>
@@ -7201,7 +6928,6 @@
           <t>尘白幻化药(Snowbreak Girl020/a_02/Girl020a_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>1</t>
@@ -7229,13 +6955,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H141" t="n">
         <v>0</v>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>ui_show_res:Girl021_01_SkeletonData&amp;ui_show_data:0.2076;0,0&amp;ui_show_idle_anim:sp_girl021_stand</t>
@@ -7249,7 +6974,6 @@
           <t>尘白幻化药(Snowbreak Girl021/01/Girl021_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>1</t>
@@ -7277,13 +7001,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>ui_show_res:Girl021_02_SkeletonData&amp;ui_show_data:0.1111;0,0&amp;ui_show_idle_anim:sp_girl021_02_gachastand</t>
@@ -7297,7 +7020,6 @@
           <t>尘白幻化药(Snowbreak Girl021/02/Girl021_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>1</t>
@@ -7325,13 +7047,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H143" t="n">
         <v>0</v>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>ui_show_res:Girl021_03_SkeletonData&amp;ui_show_data:0.0667;0,0&amp;ui_show_idle_anim:sp_girl021_03_gachastand</t>
@@ -7345,7 +7066,6 @@
           <t>尘白幻化药(Snowbreak Girl021/03/Girl021_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>1</t>
@@ -7373,13 +7093,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>ui_show_res:Girl021_SkeletonData&amp;ui_show_data:0.1154;0,0&amp;ui_show_idle_anim:sp_girl021_gachastand</t>
@@ -7393,7 +7112,6 @@
           <t>尘白幻化药(Snowbreak Girl021/Girl021/Girl021_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr">
         <is>
           <t>1</t>
@@ -7421,13 +7139,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H145" t="n">
         <v>0</v>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>ui_show_res:Girl022_01_SkeletonData&amp;ui_show_data:0.2076;0,0&amp;ui_show_idle_anim:sp_girl022_stand</t>
@@ -7441,7 +7158,6 @@
           <t>尘白幻化药(Snowbreak Girl022/01/Girl022_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>1</t>
@@ -7469,13 +7185,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>ui_show_res:Girl022_02_SkeletonData&amp;ui_show_data:0.1289;0,0&amp;ui_show_idle_anim:sp_girl022_02_gachastand</t>
@@ -7489,7 +7204,6 @@
           <t>尘白幻化药(Snowbreak Girl022/02/Girl022_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>1</t>
@@ -7517,13 +7231,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H147" t="n">
         <v>0</v>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>ui_show_res:Girl022_SkeletonData&amp;ui_show_data:0.101;0,0&amp;ui_show_idle_anim:sp_girl022_gachastand</t>
@@ -7537,7 +7250,6 @@
           <t>尘白幻化药(Snowbreak Girl022/Girl022/Girl022_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
           <t>1</t>
@@ -7565,13 +7277,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>ui_show_res:Girl023_01_SkeletonData&amp;ui_show_data:0.1704;0,0&amp;ui_show_idle_anim:sp_girl023_stand</t>
@@ -7585,7 +7296,6 @@
           <t>尘白幻化药(Snowbreak Girl023/01/Girl023_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>1</t>
@@ -7613,13 +7323,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H149" t="n">
         <v>0</v>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>ui_show_res:Girl023_02_SkeletonData&amp;ui_show_data:0.1273;0,0&amp;ui_show_idle_anim:sp_girl023_02_gachastand</t>
@@ -7633,7 +7342,6 @@
           <t>尘白幻化药(Snowbreak Girl023/02/Girl023_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>1</t>
@@ -7661,13 +7369,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H150" t="n">
         <v>0</v>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>ui_show_res:Girl023_03_SkeletonData&amp;ui_show_data:0.1457;0,0&amp;ui_show_idle_anim:sp_girl023_03_gachastand</t>
@@ -7681,7 +7388,6 @@
           <t>尘白幻化药(Snowbreak Girl023/03/Girl023_03_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>1</t>
@@ -7709,13 +7415,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>ui_show_res:Girl023_SkeletonData&amp;ui_show_data:0.1162;0,0&amp;ui_show_idle_anim:sp_girl023_gachastand</t>
@@ -7729,7 +7434,6 @@
           <t>尘白幻化药(Snowbreak Girl023/Girl023/Girl023_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>1</t>
@@ -7757,13 +7461,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>ui_show_res:Npc001_SkeletonData&amp;ui_show_data:0.2502;0,0&amp;ui_show_idle_anim:sp_npc001_stand</t>
@@ -7777,7 +7480,6 @@
           <t>尘白幻化药(Snowbreak Npc001/Npc001/Npc001_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>1</t>
@@ -7805,13 +7507,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H153" t="n">
         <v>0</v>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>ui_show_res:Npc002_SkeletonData&amp;ui_show_data:0.2522;0,0&amp;ui_show_idle_anim:sp_npc002_stand</t>
@@ -7825,7 +7526,6 @@
           <t>尘白幻化药(Snowbreak Npc002/Npc002/Npc002_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>1</t>
@@ -7853,13 +7553,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H154" t="n">
         <v>0</v>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>ui_show_res:Npc003_SkeletonData&amp;ui_show_data:0.2049;0,0&amp;ui_show_idle_anim:sp_npc003_stand</t>
@@ -7873,7 +7572,6 @@
           <t>尘白幻化药(Snowbreak Npc003/Npc003/Npc003_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>1</t>
@@ -7901,13 +7599,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H155" t="n">
         <v>0</v>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>ui_show_res:Npc004_SkeletonData&amp;ui_show_data:0.5144;0,0&amp;ui_show_idle_anim:sp_npc004_stand</t>
@@ -7921,7 +7618,6 @@
           <t>尘白幻化药(Snowbreak Npc004/Npc004/Npc004_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
           <t>1</t>
@@ -7949,13 +7645,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>ui_show_res:Npc005_SkeletonData&amp;ui_show_data:0.1836;0,0&amp;ui_show_idle_anim:sp_npc005_stand</t>
@@ -7969,7 +7664,6 @@
           <t>尘白幻化药(Snowbreak Npc005/Npc005/Npc005_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
           <t>1</t>
@@ -7997,13 +7691,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>ui_show_res:Npc006_SkeletonData&amp;ui_show_data:0.211;0,0&amp;ui_show_idle_anim:sp_npc006_stand</t>
@@ -8017,7 +7710,6 @@
           <t>尘白幻化药(Snowbreak Npc006/Npc006/Npc006_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>1</t>
@@ -8045,13 +7737,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H158" t="n">
         <v>0</v>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>ui_show_res:Npc007_SkeletonData&amp;ui_show_data:0.1909;0,0&amp;ui_show_idle_anim:sp_npc007_stand</t>
@@ -8065,7 +7756,6 @@
           <t>尘白幻化药(Snowbreak Npc007/Npc007/Npc007_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>1</t>
@@ -8093,13 +7783,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H159" t="n">
         <v>0</v>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>ui_show_res:Npc008_SkeletonData&amp;ui_show_data:0.2199;0,0&amp;ui_show_idle_anim:sp_npc008_stand</t>
@@ -8113,7 +7802,6 @@
           <t>尘白幻化药(Snowbreak Npc008/Npc008/Npc008_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
           <t>1</t>
@@ -8141,13 +7829,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H160" t="n">
         <v>0</v>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>ui_show_res:Npc009_SkeletonData&amp;ui_show_data:0.2436;0,0&amp;ui_show_idle_anim:sp_npc009_stand</t>
@@ -8161,7 +7848,6 @@
           <t>尘白幻化药(Snowbreak Npc009/Npc009/Npc009_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>1</t>
@@ -8189,13 +7875,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H161" t="n">
         <v>0</v>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>ui_show_res:Npc010_SkeletonData&amp;ui_show_data:0.1778;0,0&amp;ui_show_idle_anim:sp_npc010_stand</t>
@@ -8209,7 +7894,6 @@
           <t>尘白幻化药(Snowbreak Npc010/Npc010/Npc010_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr">
         <is>
           <t>1</t>
@@ -8237,13 +7921,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>ui_show_res:Npc011_SkeletonData&amp;ui_show_data:0.4202;0,0&amp;ui_show_idle_anim:sp_npc011_stand</t>
@@ -8257,7 +7940,6 @@
           <t>尘白幻化药(Snowbreak Npc011/Npc011/Npc011_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>1</t>
@@ -8285,13 +7967,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H163" t="n">
         <v>0</v>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>ui_show_res:Npc012_SkeletonData&amp;ui_show_data:0.2265;0,0&amp;ui_show_idle_anim:sp_npc012_stand</t>
@@ -8305,7 +7986,6 @@
           <t>尘白幻化药(Snowbreak Npc012/Npc012/Npc012_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
           <t>1</t>
@@ -8333,13 +8013,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H164" t="n">
         <v>0</v>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>ui_show_res:Npc013_SkeletonData&amp;ui_show_data:0.2247;0,0&amp;ui_show_idle_anim:sp_npc013_stand</t>
@@ -8353,7 +8032,6 @@
           <t>尘白幻化药(Snowbreak Npc013/Npc013/Npc013_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
           <t>1</t>
@@ -8381,13 +8059,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H165" t="n">
         <v>0</v>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>ui_show_res:Npc015_SkeletonData&amp;ui_show_data:0.2418;0,0&amp;ui_show_idle_anim:sp_npc015_stand</t>
@@ -8401,7 +8078,6 @@
           <t>尘白幻化药(Snowbreak Npc015/Npc015/Npc015_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
           <t>1</t>
@@ -8429,13 +8105,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H166" t="n">
         <v>0</v>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>ui_show_res:Npc016_SkeletonData&amp;ui_show_data:0.1868;0,0&amp;ui_show_idle_anim:sp_npc016_stand</t>
@@ -8449,7 +8124,6 @@
           <t>尘白幻化药(Snowbreak Npc016/Npc016/Npc016_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>1</t>
@@ -8477,13 +8151,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H167" t="n">
         <v>0</v>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>ui_show_res:Npc017_SkeletonData&amp;ui_show_data:0.2211;0,0&amp;ui_show_idle_anim:sp_npc017_stand</t>
@@ -8497,7 +8170,6 @@
           <t>尘白幻化药(Snowbreak Npc017/Npc017/Npc017_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>1</t>
@@ -8525,13 +8197,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H168" t="n">
         <v>0</v>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>ui_show_res:Npc018_SkeletonData&amp;ui_show_data:0.2274;0,0&amp;ui_show_idle_anim:sp_npc018_stand</t>
@@ -8545,7 +8216,6 @@
           <t>尘白幻化药(Snowbreak Npc018/Npc018/Npc018_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>1</t>
@@ -8573,13 +8243,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H169" t="n">
         <v>0</v>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>ui_show_res:Npc019_SkeletonData&amp;ui_show_data:0.2235;0,0&amp;ui_show_idle_anim:sp_npc019_stand</t>
@@ -8593,7 +8262,6 @@
           <t>尘白幻化药(Snowbreak Npc019/Npc019/Npc019_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>1</t>
@@ -8621,13 +8289,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H170" t="n">
         <v>0</v>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>ui_show_res:Npc020_SkeletonData&amp;ui_show_data:0.2175;0,0&amp;ui_show_idle_anim:sp_npc020_stand</t>
@@ -8641,7 +8308,6 @@
           <t>尘白幻化药(Snowbreak Npc020/Npc020/Npc020_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
           <t>1</t>
@@ -8669,13 +8335,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H171" t="n">
         <v>0</v>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>ui_show_res:Npc021_SkeletonData&amp;ui_show_data:0.2382;0,0&amp;ui_show_idle_anim:sp_npc021_stand</t>
@@ -8689,7 +8354,6 @@
           <t>尘白幻化药(Snowbreak Npc021/Npc021/Npc021_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr">
         <is>
           <t>1</t>
@@ -8717,13 +8381,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H172" t="n">
         <v>0</v>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>ui_show_res:Npc022_SkeletonData&amp;ui_show_data:0.219;0,0&amp;ui_show_idle_anim:sp_npc022_stand</t>
@@ -8737,7 +8400,6 @@
           <t>尘白幻化药(Snowbreak Npc022/Npc022/Npc022_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>1</t>
@@ -8765,13 +8427,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>ui_show_res:Npc023_SkeletonData&amp;ui_show_data:0.2294;0,0&amp;ui_show_idle_anim:sp_npc023_stand</t>
@@ -8785,7 +8446,6 @@
           <t>尘白幻化药(Snowbreak Npc023/Npc023/Npc023_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
           <t>1</t>
@@ -8813,13 +8473,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>ui_show_res:Npc024_SkeletonData&amp;ui_show_data:0.169;0,0&amp;ui_show_idle_anim:sp_npc024_stand</t>
@@ -8833,7 +8492,6 @@
           <t>尘白幻化药(Snowbreak Npc024/Npc024/Npc024_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>1</t>
@@ -8861,13 +8519,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H175" t="n">
         <v>0</v>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>ui_show_res:Npc026_SkeletonData&amp;ui_show_data:0.2196;0,0&amp;ui_show_idle_anim:sp_npc026_stand</t>
@@ -8881,7 +8538,6 @@
           <t>尘白幻化药(Snowbreak Npc026/Npc026/Npc026_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr">
         <is>
           <t>1</t>
@@ -8909,13 +8565,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>ui_show_res:Npc028_SkeletonData&amp;ui_show_data:0.2481;0,0&amp;ui_show_idle_anim:sp_npc001_stand</t>
@@ -8929,7 +8584,6 @@
           <t>尘白幻化药(Snowbreak Npc028/Npc028/Npc028_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr">
         <is>
           <t>1</t>
@@ -8957,13 +8611,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H177" t="n">
         <v>0</v>
       </c>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>ui_show_res:Npc29_02_SkeletonData&amp;ui_show_data:0.2215;0,0&amp;ui_show_idle_anim:sp_npc029_02_stand</t>
@@ -8977,7 +8630,6 @@
           <t>尘白幻化药(Snowbreak Npc29/02/Npc29_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr">
         <is>
           <t>1</t>
@@ -9005,13 +8657,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H178" t="n">
         <v>0</v>
       </c>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>ui_show_res:Npc029_SkeletonData&amp;ui_show_data:0.1966;0,0&amp;ui_show_idle_anim:sp_npc029_stand</t>
@@ -9025,7 +8676,6 @@
           <t>尘白幻化药(Snowbreak Npc029/Npc029/Npc029_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr">
         <is>
           <t>1</t>
@@ -9053,13 +8703,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H179" t="n">
         <v>0</v>
       </c>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>ui_show_res:Npc030_SkeletonData&amp;ui_show_data:0.1711;0,0&amp;ui_show_idle_anim:sp_npc030_stand</t>
@@ -9073,7 +8722,6 @@
           <t>尘白幻化药(Snowbreak Npc030/Npc030/Npc030_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr">
         <is>
           <t>1</t>
@@ -9101,13 +8749,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H180" t="n">
         <v>0</v>
       </c>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>ui_show_res:Npc031_SkeletonData&amp;ui_show_data:0.1885;0,0&amp;ui_show_idle_anim:sp_npc031_stand</t>
@@ -9121,7 +8768,6 @@
           <t>尘白幻化药(Snowbreak Npc031/Npc031/Npc031_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr">
         <is>
           <t>1</t>
@@ -9149,13 +8795,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>ui_show_res:Npc032_SkeletonData&amp;ui_show_data:0.2191;0,0&amp;ui_show_idle_anim:sp_npc032_stand</t>
@@ -9169,7 +8814,6 @@
           <t>尘白幻化药(Snowbreak Npc032/Npc032/Npc032_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr">
         <is>
           <t>1</t>
@@ -9197,13 +8841,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H182" t="n">
         <v>0</v>
       </c>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>ui_show_res:Npc033_SkeletonData&amp;ui_show_data:0.2042;0,0&amp;ui_show_idle_anim:sp_npc033_stand</t>
@@ -9217,7 +8860,6 @@
           <t>尘白幻化药(Snowbreak Npc033/Npc033/Npc033_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr">
         <is>
           <t>1</t>
@@ -9245,13 +8887,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H183" t="n">
         <v>0</v>
       </c>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>ui_show_res:Npc034_01_SkeletonData&amp;ui_show_data:0.2421;0,0&amp;ui_show_idle_anim:sp_npc034_stand</t>
@@ -9265,7 +8906,6 @@
           <t>尘白幻化药(Snowbreak Npc034/01/Npc034_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr">
         <is>
           <t>1</t>
@@ -9293,13 +8933,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H184" t="n">
         <v>0</v>
       </c>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>ui_show_res:Npc034_SkeletonData&amp;ui_show_data:0.2421;0,0&amp;ui_show_idle_anim:sp_npc034_stand</t>
@@ -9313,7 +8952,6 @@
           <t>尘白幻化药(Snowbreak Npc034/Npc034/Npc034_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr">
         <is>
           <t>1</t>
@@ -9341,13 +8979,12 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H185" t="n">
         <v>0</v>
       </c>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>ui_show_res:Npc035_01_SkeletonData&amp;ui_show_data:0.1981;0,0&amp;ui_show_idle_anim:sp_npc035_stand</t>
@@ -9361,7 +8998,6 @@
           <t>尘白幻化药(Snowbreak Npc035/01/Npc035_01_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr">
         <is>
           <t>1</t>
@@ -9389,13 +9025,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>ui_show_res:Npc035_SkeletonData&amp;ui_show_data:0.2222;0,0&amp;ui_show_idle_anim:sp_npc035_stand</t>
@@ -9409,7 +9044,6 @@
           <t>尘白幻化药(Snowbreak Npc035/Npc035/Npc035_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>1</t>
@@ -9437,13 +9071,12 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H187" t="n">
         <v>0</v>
       </c>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>ui_show_res:Npc036_SkeletonData&amp;ui_show_data:0.2145;0,0&amp;ui_show_idle_anim:sp_npc036_stand</t>
@@ -9457,7 +9090,6 @@
           <t>尘白幻化药(Snowbreak Npc036/Npc036/Npc036_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>1</t>
@@ -9485,13 +9117,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H188" t="n">
         <v>0</v>
       </c>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>ui_show_res:Npc037_SkeletonData&amp;ui_show_data:0.2179;0,0&amp;ui_show_idle_anim:sp_npc037_stand</t>
@@ -9505,7 +9136,6 @@
           <t>尘白幻化药(Snowbreak Npc037/Npc037/Npc037_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>1</t>
@@ -9533,13 +9163,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H189" t="n">
         <v>0</v>
       </c>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>ui_show_res:Npc038_SkeletonData&amp;ui_show_data:0.2106;0,0&amp;ui_show_idle_anim:sp_npc038_stand</t>
@@ -9553,7 +9182,6 @@
           <t>尘白幻化药(Snowbreak Npc038/Npc038/Npc038_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
           <t>1</t>
@@ -9581,13 +9209,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H190" t="n">
         <v>0</v>
       </c>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>ui_show_res:Npc039_SkeletonData&amp;ui_show_data:0.1819;0,0&amp;ui_show_idle_anim:sp_npc039_stand</t>
@@ -9601,7 +9228,6 @@
           <t>尘白幻化药(Snowbreak Npc039/Npc039/Npc039_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
           <t>1</t>
@@ -9629,13 +9255,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H191" t="n">
         <v>0</v>
       </c>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>ui_show_res:Npc040_SkeletonData&amp;ui_show_data:0.1978;0,0&amp;ui_show_idle_anim:sp_npc040_stand</t>
@@ -9649,7 +9274,6 @@
           <t>尘白幻化药(Snowbreak Npc040/Npc040/Npc040_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr">
         <is>
           <t>1</t>
@@ -9677,13 +9301,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H192" t="n">
         <v>0</v>
       </c>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>ui_show_res:Npc041_SkeletonData&amp;ui_show_data:0.2202;0,0&amp;ui_show_idle_anim:sp_npc041_stand</t>
@@ -9697,7 +9320,6 @@
           <t>尘白幻化药(Snowbreak Npc041/Npc041/Npc041_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr">
         <is>
           <t>1</t>
@@ -9725,13 +9347,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H193" t="n">
         <v>0</v>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>ui_show_res:Npc042_SkeletonData&amp;ui_show_data:0.2279;0,0&amp;ui_show_idle_anim:sp_npc042_stand</t>
@@ -9745,7 +9366,6 @@
           <t>尘白幻化药(Snowbreak Npc042/Npc042/Npc042_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr">
         <is>
           <t>1</t>
@@ -9773,13 +9393,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H194" t="n">
         <v>0</v>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>ui_show_res:Npc043_SkeletonData&amp;ui_show_data:0.1841;0,0&amp;ui_show_idle_anim:sp_npc043_stand</t>
@@ -9793,7 +9412,6 @@
           <t>尘白幻化药(Snowbreak Npc043/Npc043/Npc043_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
           <t>1</t>
@@ -9821,13 +9439,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>ui_show_res:Npc044_SkeletonData&amp;ui_show_data:0.1863;0,0&amp;ui_show_idle_anim:sp_npc044_stand</t>
@@ -9841,7 +9458,6 @@
           <t>尘白幻化药(Snowbreak Npc044/Npc044/Npc044_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>1</t>
@@ -9869,13 +9485,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H196" t="n">
         <v>0</v>
       </c>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>ui_show_res:Npc045_SkeletonData&amp;ui_show_data:0.2211;0,0&amp;ui_show_idle_anim:sp_npc017_stand</t>
@@ -9889,7 +9504,6 @@
           <t>尘白幻化药(Snowbreak Npc045/Npc045/Npc045_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>1</t>
@@ -9917,13 +9531,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H197" t="n">
         <v>0</v>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>ui_show_res:Npc046_SkeletonData&amp;ui_show_data:0.1758;0,0&amp;ui_show_idle_anim:sp_npc046_stand</t>
@@ -9937,7 +9550,6 @@
           <t>尘白幻化药(Snowbreak Npc046/Npc046/Npc046_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>1</t>
@@ -9965,13 +9577,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H198" t="n">
         <v>0</v>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>ui_show_res:Npc047_SkeletonData&amp;ui_show_data:0.2284;0,0&amp;ui_show_idle_anim:sp_npc047_stand</t>
@@ -9985,7 +9596,6 @@
           <t>尘白幻化药(Snowbreak Npc047/Npc047/Npc047_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>1</t>
@@ -10013,13 +9623,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H199" t="n">
         <v>0</v>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>ui_show_res:Npc048_SkeletonData&amp;ui_show_data:0.187;0,0&amp;ui_show_idle_anim:sp_npc048_stand</t>
@@ -10033,7 +9642,6 @@
           <t>尘白幻化药(Snowbreak Npc048/Npc048/Npc048_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>1</t>
@@ -10061,13 +9669,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H200" t="n">
         <v>0</v>
       </c>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>ui_show_res:Npc049_SkeletonData&amp;ui_show_data:0.1842;0,0&amp;ui_show_idle_anim:sp_npc049_stand</t>
@@ -10081,7 +9688,6 @@
           <t>尘白幻化药(Snowbreak Npc049/Npc049/Npc049_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>1</t>
@@ -10109,13 +9715,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H201" t="n">
         <v>0</v>
       </c>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>ui_show_res:Npc051_SkeletonData&amp;ui_show_data:0.1728;0,0&amp;ui_show_idle_anim:sp_npc051_stand</t>
@@ -10129,7 +9734,6 @@
           <t>尘白幻化药(Snowbreak Npc051/Npc051/Npc051_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr">
         <is>
           <t>1</t>
@@ -10157,13 +9761,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H202" t="n">
         <v>0</v>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>ui_show_res:Npc052_SkeletonData&amp;ui_show_data:0.2026;0,0&amp;ui_show_idle_anim:sp_npc052_stand</t>
@@ -10177,7 +9780,6 @@
           <t>尘白幻化药(Snowbreak Npc052/Npc052/Npc052_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
           <t>1</t>
@@ -10205,13 +9807,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H203" t="n">
         <v>0</v>
       </c>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>ui_show_res:Npc053_SkeletonData&amp;ui_show_data:0.2105;0,0&amp;ui_show_idle_anim:sp_npc053_stand</t>
@@ -10225,7 +9826,6 @@
           <t>尘白幻化药(Snowbreak Npc053/Npc053/Npc053_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr">
         <is>
           <t>1</t>
@@ -10253,13 +9853,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H204" t="n">
         <v>0</v>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>ui_show_res:Npc054_SkeletonData&amp;ui_show_data:0.1862;0,0&amp;ui_show_idle_anim:sp_npc054_stand</t>
@@ -10273,7 +9872,6 @@
           <t>尘白幻化药(Snowbreak Npc054/Npc054/Npc054_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>1</t>
@@ -10301,13 +9899,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H205" t="n">
         <v>0</v>
       </c>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>ui_show_res:Npc055_SkeletonData&amp;ui_show_data:0.2294;0,0&amp;ui_show_idle_anim:sp_npc055_stand</t>
@@ -10321,7 +9918,6 @@
           <t>尘白幻化药(Snowbreak Npc055/Npc055/Npc055_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr">
         <is>
           <t>1</t>
@@ -10349,13 +9945,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H206" t="n">
         <v>0</v>
       </c>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>ui_show_res:Npc056_SkeletonData&amp;ui_show_data:0.1686;0,0&amp;ui_show_idle_anim:sp_npc056_stand</t>
@@ -10369,7 +9964,6 @@
           <t>尘白幻化药(Snowbreak Npc056/Npc056/Npc056_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr">
         <is>
           <t>1</t>
@@ -10397,13 +9991,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H207" t="n">
         <v>0</v>
       </c>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>ui_show_res:Npc057_SkeletonData&amp;ui_show_data:0.1722;0,0&amp;ui_show_idle_anim:sp_npc057_stand</t>
@@ -10417,7 +10010,6 @@
           <t>尘白幻化药(Snowbreak Npc057/Npc057/Npc057_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
           <t>1</t>
@@ -10445,13 +10037,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H208" t="n">
         <v>0</v>
       </c>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>ui_show_res:Npc058_SkeletonData&amp;ui_show_data:0.2068;0,0&amp;ui_show_idle_anim:sp_npc058_stand</t>
@@ -10465,7 +10056,6 @@
           <t>尘白幻化药(Snowbreak Npc058/Npc058/Npc058_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr">
         <is>
           <t>1</t>
@@ -10493,13 +10083,12 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H209" t="n">
         <v>0</v>
       </c>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>ui_show_res:Npc059_SkeletonData&amp;ui_show_data:0.2489;0,0&amp;ui_show_idle_anim:sp_npc059_stand</t>
@@ -10513,7 +10102,6 @@
           <t>尘白幻化药(Snowbreak Npc059/Npc059/Npc059_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr">
         <is>
           <t>1</t>
@@ -10541,13 +10129,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H210" t="n">
         <v>0</v>
       </c>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>ui_show_res:Npc060_SkeletonData&amp;ui_show_data:0.2489;0,0&amp;ui_show_idle_anim:sp_npc060_stand</t>
@@ -10561,7 +10148,6 @@
           <t>尘白幻化药(Snowbreak Npc060/Npc060/Npc060_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr">
         <is>
           <t>1</t>
@@ -10589,13 +10175,12 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H211" t="n">
         <v>0</v>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>ui_show_res:Npc061_SkeletonData&amp;ui_show_data:0.1902;0,0&amp;ui_show_idle_anim:sp_npc061_stand</t>
@@ -10609,7 +10194,6 @@
           <t>尘白幻化药(Snowbreak Npc061/Npc061/Npc061_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr">
         <is>
           <t>1</t>
@@ -10637,13 +10221,12 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H212" t="n">
         <v>0</v>
       </c>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>ui_show_res:Npc062_SkeletonData&amp;ui_show_data:0.2207;0,0&amp;ui_show_idle_anim:sp_npc062_stand</t>
@@ -10657,7 +10240,6 @@
           <t>尘白幻化药(Snowbreak Npc062/Npc062/Npc062_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
           <t>1</t>
@@ -10685,13 +10267,12 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H213" t="n">
         <v>0</v>
       </c>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>ui_show_res:Npc063_SkeletonData&amp;ui_show_data:0.1785;0,0&amp;ui_show_idle_anim:sp_npc063_stand</t>
@@ -10705,7 +10286,6 @@
           <t>尘白幻化药(Snowbreak Npc063/Npc063/Npc063_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr">
         <is>
           <t>1</t>
@@ -10733,13 +10313,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H214" t="n">
         <v>0</v>
       </c>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>ui_show_res:Npc064_SkeletonData&amp;ui_show_data:0.1335;0,0&amp;ui_show_idle_anim:sp_npc064_stand</t>
@@ -10753,7 +10332,6 @@
           <t>尘白幻化药(Snowbreak Npc064/Npc064/Npc064_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr">
         <is>
           <t>1</t>
@@ -10781,13 +10359,12 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H215" t="n">
         <v>0</v>
       </c>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>ui_show_res:Npc065_SkeletonData&amp;ui_show_data:0.2383;0,0&amp;ui_show_idle_anim:sp_npc065_stand</t>
@@ -10801,7 +10378,6 @@
           <t>尘白幻化药(Snowbreak Npc065/Npc065/Npc065_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr">
         <is>
           <t>1</t>
@@ -10829,13 +10405,12 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H216" t="n">
         <v>0</v>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>ui_show_res:Npc067_SkeletonData&amp;ui_show_data:0.1968;0,0&amp;ui_show_idle_anim:sp_npc067_stand</t>
@@ -10849,7 +10424,6 @@
           <t>尘白幻化药(Snowbreak Npc067/Npc067/Npc067_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr">
         <is>
           <t>1</t>
@@ -10877,13 +10451,12 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H217" t="n">
         <v>0</v>
       </c>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>ui_show_res:Npc068_SkeletonData&amp;ui_show_data:0.2247;0,0&amp;ui_show_idle_anim:sp_npc068_stand</t>
@@ -10897,7 +10470,6 @@
           <t>尘白幻化药(Snowbreak Npc068/Npc068/Npc068_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr">
         <is>
           <t>1</t>
@@ -10925,13 +10497,12 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H218" t="n">
         <v>0</v>
       </c>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>ui_show_res:Npc069_02_SkeletonData&amp;ui_show_data:0.1991;0,0&amp;ui_show_idle_anim:sp_npc069_stand</t>
@@ -10945,7 +10516,6 @@
           <t>尘白幻化药(Snowbreak Npc069/02/Npc069_02_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>1</t>
@@ -10973,13 +10543,12 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H219" t="n">
         <v>0</v>
       </c>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>ui_show_res:Npc069_SkeletonData&amp;ui_show_data:0.1903;0,0&amp;ui_show_idle_anim:sp_npc069_stand</t>
@@ -10993,7 +10562,6 @@
           <t>尘白幻化药(Snowbreak Npc069/Npc069/Npc069_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr">
         <is>
           <t>1</t>
@@ -11021,13 +10589,12 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H220" t="n">
         <v>0</v>
       </c>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>ui_show_res:Npc070_SkeletonData&amp;ui_show_data:0.1795;0,0&amp;ui_show_idle_anim:sp_npc070_stand</t>
@@ -11041,7 +10608,6 @@
           <t>尘白幻化药(Snowbreak Npc070/Npc070/Npc070_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr">
         <is>
           <t>1</t>
@@ -11069,13 +10635,12 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H221" t="n">
         <v>0</v>
       </c>
-      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>ui_show_res:Npc071_SkeletonData&amp;ui_show_data:0.215;0,0&amp;ui_show_idle_anim:sp_npc071_stand</t>
@@ -11089,7 +10654,6 @@
           <t>尘白幻化药(Snowbreak Npc071/Npc071/Npc071_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr">
         <is>
           <t>1</t>
@@ -11117,13 +10681,12 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H222" t="n">
         <v>0</v>
       </c>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>ui_show_res:Npc072_SkeletonData&amp;ui_show_data:0.2042;0,0&amp;ui_show_idle_anim:sp_npc072_stand</t>
@@ -11137,7 +10700,6 @@
           <t>尘白幻化药(Snowbreak Npc072/Npc072/Npc072_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
         <is>
           <t>1</t>
@@ -11165,13 +10727,12 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H223" t="n">
         <v>0</v>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>ui_show_res:Npc073_SkeletonData&amp;ui_show_data:0.1811;0,0&amp;ui_show_idle_anim:sp_npc073_stand</t>
@@ -11185,7 +10746,6 @@
           <t>尘白幻化药(Snowbreak Npc073/Npc073/Npc073_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr">
         <is>
           <t>1</t>
@@ -11213,13 +10773,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H224" t="n">
         <v>0</v>
       </c>
-      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>ui_show_res:Npc074_SkeletonData&amp;ui_show_data:0.1967;0,0&amp;ui_show_idle_anim:sp_npc074_stand</t>
@@ -11233,7 +10792,6 @@
           <t>尘白幻化药(Snowbreak Npc074/Npc074/Npc074_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr">
         <is>
           <t>1</t>
@@ -11261,13 +10819,12 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H225" t="n">
         <v>0</v>
       </c>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>ui_show_res:Npc076_SkeletonData&amp;ui_show_data:0.2294;0,0&amp;ui_show_idle_anim:sp_npc076_stand</t>
@@ -11281,7 +10838,6 @@
           <t>尘白幻化药(Snowbreak Npc076/Npc076/Npc076_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr">
         <is>
           <t>1</t>
@@ -11309,13 +10865,12 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H226" t="n">
         <v>0</v>
       </c>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>ui_show_res:Npc077_SkeletonData&amp;ui_show_data:0.2292;0,0&amp;ui_show_idle_anim:sp_npc071_stand</t>
@@ -11329,7 +10884,6 @@
           <t>尘白幻化药(Snowbreak Npc077/Npc077/Npc077_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr">
         <is>
           <t>1</t>
@@ -11357,13 +10911,12 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H227" t="n">
         <v>0</v>
       </c>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>ui_show_res:Npc078_SkeletonData&amp;ui_show_data:0.1782;0,0&amp;ui_show_idle_anim:sp_npc078_stand</t>
@@ -11377,7 +10930,6 @@
           <t>尘白幻化药(Snowbreak Npc078/Npc078/Npc078_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>1</t>
@@ -11405,13 +10957,12 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H228" t="n">
         <v>0</v>
       </c>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>ui_show_res:Npc081_SkeletonData&amp;ui_show_data:0.2753;0,0&amp;ui_show_idle_anim:sp_npc081_stand</t>
@@ -11425,7 +10976,6 @@
           <t>尘白幻化药(Snowbreak Npc081/Npc081/Npc081_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>1</t>
@@ -11453,13 +11003,12 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H229" t="n">
         <v>0</v>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>ui_show_res:Npc082_SkeletonData&amp;ui_show_data:0.1747;0,0&amp;ui_show_idle_anim:sp_npc082_stand</t>
@@ -11473,7 +11022,6 @@
           <t>尘白幻化药(Snowbreak Npc082/Npc082/Npc082_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>1</t>
@@ -11501,13 +11049,12 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H230" t="n">
         <v>0</v>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>ui_show_res:Npc083_SkeletonData&amp;ui_show_data:0.1306;0,0&amp;ui_show_idle_anim:sp_npc083_stand</t>
@@ -11521,7 +11068,6 @@
           <t>尘白幻化药(Snowbreak Npc083/Npc083/Npc083_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr">
         <is>
           <t>1</t>
@@ -11549,13 +11095,12 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H231" t="n">
         <v>0</v>
       </c>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>ui_show_res:Npc084_SkeletonData&amp;ui_show_data:0.2441;0,0&amp;ui_show_idle_anim:sp_npc084_stand</t>
@@ -11569,7 +11114,6 @@
           <t>尘白幻化药(Snowbreak Npc084/Npc084/Npc084_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr">
         <is>
           <t>1</t>
@@ -11597,13 +11141,12 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H232" t="n">
         <v>0</v>
       </c>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>ui_show_res:Npc085_SkeletonData&amp;ui_show_data:0.1934;0,0&amp;ui_show_idle_anim:sp_npc085</t>
@@ -11617,7 +11160,6 @@
           <t>尘白幻化药(Snowbreak Npc085/Npc085/Npc085_SkeletonData.asset stand链:首个动画兜底)</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr">
         <is>
           <t>1</t>
@@ -11645,13 +11187,12 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H233" t="n">
         <v>0</v>
       </c>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>ui_show_res:Npc086_SkeletonData&amp;ui_show_data:0.1955;0,0&amp;ui_show_idle_anim:sp_npc086_stand</t>
@@ -11665,7 +11206,6 @@
           <t>尘白幻化药(Snowbreak Npc086/Npc086/Npc086_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr">
         <is>
           <t>1</t>
@@ -11693,13 +11233,12 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H234" t="n">
         <v>0</v>
       </c>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>ui_show_res:Npc087_SkeletonData&amp;ui_show_data:0.1872;0,0&amp;ui_show_idle_anim:sp_npc087_stand</t>
@@ -11713,7 +11252,6 @@
           <t>尘白幻化药(Snowbreak Npc087/Npc087/Npc087_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr">
         <is>
           <t>1</t>
@@ -11741,13 +11279,12 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H235" t="n">
         <v>0</v>
       </c>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>ui_show_res:Npc088_SkeletonData&amp;ui_show_data:0.2551;0,0&amp;ui_show_idle_anim:sp_npc088_stand</t>
@@ -11761,7 +11298,6 @@
           <t>尘白幻化药(Snowbreak Npc088/Npc088/Npc088_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr">
         <is>
           <t>1</t>
@@ -11789,13 +11325,12 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H236" t="n">
         <v>0</v>
       </c>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>ui_show_res:Npc089_SkeletonData&amp;ui_show_data:0.2317;0,0&amp;ui_show_idle_anim:sp_npc089_stand</t>
@@ -11809,7 +11344,6 @@
           <t>尘白幻化药(Snowbreak Npc089/Npc089/Npc089_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr">
         <is>
           <t>1</t>
@@ -11837,13 +11371,12 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H237" t="n">
         <v>0</v>
       </c>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>ui_show_res:Npc090_SkeletonData&amp;ui_show_data:0.1425;0,0&amp;ui_show_idle_anim:sp_boss402_stand</t>
@@ -11857,7 +11390,6 @@
           <t>尘白幻化药(Snowbreak Npc090/Npc090/Npc090_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr">
         <is>
           <t>1</t>
@@ -11885,13 +11417,12 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H238" t="n">
         <v>0</v>
       </c>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>ui_show_res:Npc091_SkeletonData&amp;ui_show_data:0.195;0,0&amp;ui_show_idle_anim:sp_npc091_stand</t>
@@ -11905,7 +11436,6 @@
           <t>尘白幻化药(Snowbreak Npc091/Npc091/Npc091_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr">
         <is>
           <t>1</t>
@@ -11933,13 +11463,12 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H239" t="n">
         <v>0</v>
       </c>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>ui_show_res:Npc092_SkeletonData&amp;ui_show_data:0.2363;0,0&amp;ui_show_idle_anim:sp_npc092_stand</t>
@@ -11953,7 +11482,6 @@
           <t>尘白幻化药(Snowbreak Npc092/Npc092/Npc092_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr">
         <is>
           <t>1</t>
@@ -11981,13 +11509,12 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H240" t="n">
         <v>0</v>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>ui_show_res:Npc093_SkeletonData&amp;ui_show_data:0.2149;0,0&amp;ui_show_idle_anim:sp_npc093_stand</t>
@@ -12001,7 +11528,6 @@
           <t>尘白幻化药(Snowbreak Npc093/Npc093/Npc093_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr">
         <is>
           <t>1</t>
@@ -12029,13 +11555,12 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H241" t="n">
         <v>0</v>
       </c>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>ui_show_res:Npc094_SkeletonData&amp;ui_show_data:0.2233;0,0&amp;ui_show_idle_anim:sp_npc094_stand</t>
@@ -12049,7 +11574,6 @@
           <t>尘白幻化药(Snowbreak Npc094/Npc094/Npc094_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr">
         <is>
           <t>1</t>
@@ -12077,13 +11601,12 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H242" t="n">
         <v>0</v>
       </c>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>ui_show_res:Npc095_SkeletonData&amp;ui_show_data:0.2011;0,0&amp;ui_show_idle_anim:sp_npc090_stand</t>
@@ -12097,7 +11620,6 @@
           <t>尘白幻化药(Snowbreak Npc095/Npc095/Npc095_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr">
         <is>
           <t>1</t>
@@ -12125,13 +11647,12 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H243" t="n">
         <v>0</v>
       </c>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>ui_show_res:Npc096_SkeletonData&amp;ui_show_data:0.2149;0,0&amp;ui_show_idle_anim:sp_npc093_stand</t>
@@ -12145,7 +11666,6 @@
           <t>尘白幻化药(Snowbreak Npc096/Npc096/Npc096_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr">
         <is>
           <t>1</t>
@@ -12173,13 +11693,12 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H244" t="n">
         <v>0</v>
       </c>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>ui_show_res:Npc097_SkeletonData&amp;ui_show_data:0.1985;0,0&amp;ui_show_idle_anim:sp_npc097_stand</t>
@@ -12193,7 +11712,6 @@
           <t>尘白幻化药(Snowbreak Npc097/Npc097/Npc097_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr">
         <is>
           <t>1</t>
@@ -12221,13 +11739,12 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H245" t="n">
         <v>0</v>
       </c>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>ui_show_res:Npc098_SkeletonData&amp;ui_show_data:0.1704;0,0&amp;ui_show_idle_anim:sp_npc098_stand</t>
@@ -12241,7 +11758,6 @@
           <t>尘白幻化药(Snowbreak Npc098/Npc098/Npc098_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr">
         <is>
           <t>1</t>
@@ -12269,13 +11785,12 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H246" t="n">
         <v>0</v>
       </c>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>ui_show_res:Npc099_SkeletonData&amp;ui_show_data:0.1335;0,0&amp;ui_show_idle_anim:sp_npc099_stand</t>
@@ -12289,7 +11804,6 @@
           <t>尘白幻化药(Snowbreak Npc099/Npc099/Npc099_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr">
         <is>
           <t>1</t>
@@ -12317,13 +11831,12 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H247" t="n">
         <v>0</v>
       </c>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>ui_show_res:Npc100_SkeletonData&amp;ui_show_data:0.2149;0,0&amp;ui_show_idle_anim:sp_npc100_stand</t>
@@ -12337,7 +11850,6 @@
           <t>尘白幻化药(Snowbreak Npc100/Npc100/Npc100_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr">
         <is>
           <t>1</t>
@@ -12365,13 +11877,12 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H248" t="n">
         <v>0</v>
       </c>
-      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>ui_show_res:Npc101_SkeletonData&amp;ui_show_data:0.2418;0,0&amp;ui_show_idle_anim:sp_npc101_stand</t>
@@ -12385,7 +11896,6 @@
           <t>尘白幻化药(Snowbreak Npc101/Npc101/Npc101_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr">
         <is>
           <t>1</t>
@@ -12413,13 +11923,12 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H249" t="n">
         <v>0</v>
       </c>
-      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>ui_show_res:Npc102_SkeletonData&amp;ui_show_data:0.2418;0,0&amp;ui_show_idle_anim:sp_npc102_stand</t>
@@ -12433,7 +11942,6 @@
           <t>尘白幻化药(Snowbreak Npc102/Npc102/Npc102_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr">
         <is>
           <t>1</t>
@@ -12461,13 +11969,12 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H250" t="n">
         <v>0</v>
       </c>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>ui_show_res:Npc103_SkeletonData&amp;ui_show_data:0.2418;0,0&amp;ui_show_idle_anim:sp_npc103_stand</t>
@@ -12481,7 +11988,6 @@
           <t>尘白幻化药(Snowbreak Npc103/Npc103/Npc103_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr">
         <is>
           <t>1</t>
@@ -12509,13 +12015,12 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H251" t="n">
         <v>0</v>
       </c>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>ui_show_res:Npc104_SkeletonData&amp;ui_show_data:0.2235;0,0&amp;ui_show_idle_anim:sp_npc104_stand</t>
@@ -12529,7 +12034,6 @@
           <t>尘白幻化药(Snowbreak Npc104/Npc104/Npc104_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr">
         <is>
           <t>1</t>
@@ -12557,13 +12061,12 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H252" t="n">
         <v>0</v>
       </c>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>ui_show_res:Npc105_SkeletonData&amp;ui_show_data:0.1251;0,0&amp;ui_show_idle_anim:sp_npc105_stand</t>
@@ -12577,7 +12080,6 @@
           <t>尘白幻化药(Snowbreak Npc105/Npc105/Npc105_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr">
         <is>
           <t>1</t>
@@ -12605,13 +12107,12 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H253" t="n">
         <v>0</v>
       </c>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>ui_show_res:Npc106_SkeletonData&amp;ui_show_data:0.1955;0,0&amp;ui_show_idle_anim:sp_npc106_stand</t>
@@ -12625,7 +12126,6 @@
           <t>尘白幻化药(Snowbreak Npc106/Npc106/Npc106_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr">
         <is>
           <t>1</t>
@@ -12653,13 +12153,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H254" t="n">
         <v>0</v>
       </c>
-      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>ui_show_res:Npc107_SkeletonData&amp;ui_show_data:0.1606;0,0&amp;ui_show_idle_anim:sp_npc107_stand</t>
@@ -12673,7 +12172,6 @@
           <t>尘白幻化药(Snowbreak Npc107/Npc107/Npc107_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr">
         <is>
           <t>1</t>
@@ -12701,13 +12199,12 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H255" t="n">
         <v>0</v>
       </c>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>ui_show_res:Npc108_SkeletonData&amp;ui_show_data:0.4202;0,0&amp;ui_show_idle_anim:sp_npc011_stand</t>
@@ -12721,7 +12218,6 @@
           <t>尘白幻化药(Snowbreak Npc108/Npc108/Npc108_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr">
         <is>
           <t>1</t>
@@ -12749,13 +12245,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H256" t="n">
         <v>0</v>
       </c>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>ui_show_res:Npc109_SkeletonData&amp;ui_show_data:0.1364;0,0&amp;ui_show_idle_anim:sp_npc109_stand</t>
@@ -12769,7 +12264,6 @@
           <t>尘白幻化药(Snowbreak Npc109/Npc109/Npc109_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr">
         <is>
           <t>1</t>
@@ -12797,13 +12291,12 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H257" t="n">
         <v>0</v>
       </c>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>ui_show_res:Npc110_SkeletonData&amp;ui_show_data:0.1356;0,0&amp;ui_show_idle_anim:sp_npc110_stand</t>
@@ -12817,7 +12310,6 @@
           <t>尘白幻化药(Snowbreak Npc110/Npc110/Npc110_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr">
         <is>
           <t>1</t>
@@ -12845,13 +12337,12 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Item_TransformPotion_1</t>
+          <t>Item_Potion_1</t>
         </is>
       </c>
       <c r="H258" t="n">
         <v>0</v>
       </c>
-      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>ui_show_res:Npc111_SkeletonData&amp;ui_show_data:0.2057;0,0&amp;ui_show_idle_anim:sp_npc111_stand</t>
@@ -12865,7 +12356,6 @@
           <t>尘白幻化药(Snowbreak Npc111/Npc111/Npc111_SkeletonData.asset stand链:stand结尾)</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr">
         <is>
           <t>1</t>
